--- a/output/roomself_excel/5581.xlsx
+++ b/output/roomself_excel/5581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>115170</v>
+        <v>207580</v>
       </c>
       <c r="D2" t="n">
-        <v>2716</v>
+        <v>3652</v>
       </c>
       <c r="E2" t="n">
-        <v>379</v>
+        <v>518</v>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>163020</v>
+        <v>243256</v>
       </c>
       <c r="D3" t="n">
-        <v>5132</v>
+        <v>4252</v>
       </c>
       <c r="E3" t="n">
-        <v>143</v>
+        <v>544</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>108855</v>
+        <v>115170</v>
       </c>
       <c r="D4" t="n">
-        <v>2656</v>
+        <v>2716</v>
       </c>
       <c r="E4" t="n">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="F4" t="n">
-        <v>324</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>109237</v>
+        <v>108855</v>
       </c>
       <c r="D5" t="n">
-        <v>2648</v>
+        <v>2656</v>
       </c>
       <c r="E5" t="n">
-        <v>313</v>
+        <v>398</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>110035</v>
+        <v>109237</v>
       </c>
       <c r="D6" t="n">
-        <v>2672</v>
+        <v>2648</v>
       </c>
       <c r="E6" t="n">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>45570</v>
+        <v>110035</v>
       </c>
       <c r="D7" t="n">
-        <v>1724</v>
+        <v>2672</v>
       </c>
       <c r="E7" t="n">
-        <v>245</v>
+        <v>373</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28728</v>
+        <v>110920</v>
       </c>
       <c r="D8" t="n">
-        <v>1364</v>
+        <v>2684</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>110920</v>
+        <v>111000</v>
       </c>
       <c r="D9" t="n">
         <v>2684</v>
       </c>
       <c r="E9" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15960</v>
+        <v>110704</v>
       </c>
       <c r="D10" t="n">
-        <v>1028</v>
+        <v>2680</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40734</v>
+        <v>112346</v>
       </c>
       <c r="D11" t="n">
-        <v>1620</v>
+        <v>2700</v>
       </c>
       <c r="E11" t="n">
-        <v>219</v>
+        <v>377</v>
       </c>
       <c r="F11" t="n">
-        <v>170</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24016</v>
+        <v>110558</v>
       </c>
       <c r="D12" t="n">
-        <v>1240</v>
+        <v>2676</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>646448</v>
+        <v>45570</v>
       </c>
       <c r="D13" t="n">
-        <v>11504</v>
+        <v>1724</v>
       </c>
       <c r="E13" t="n">
-        <v>1001</v>
+        <v>245</v>
       </c>
       <c r="F13" t="n">
-        <v>518</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>93066</v>
+        <v>15960</v>
       </c>
       <c r="D14" t="n">
-        <v>2768</v>
+        <v>1028</v>
       </c>
       <c r="E14" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11970</v>
+        <v>24016</v>
       </c>
       <c r="D15" t="n">
-        <v>892</v>
+        <v>1240</v>
       </c>
       <c r="E15" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>111000</v>
+        <v>17442</v>
       </c>
       <c r="D16" t="n">
-        <v>2684</v>
+        <v>1092</v>
       </c>
       <c r="E16" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>110704</v>
+        <v>26068</v>
       </c>
       <c r="D17" t="n">
-        <v>2680</v>
+        <v>1316</v>
       </c>
       <c r="E17" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17442</v>
+        <v>17484</v>
       </c>
       <c r="D18" t="n">
-        <v>1092</v>
+        <v>1060</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26068</v>
+        <v>13113</v>
       </c>
       <c r="D19" t="n">
-        <v>1316</v>
+        <v>936</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>108537</v>
+        <v>26130</v>
       </c>
       <c r="D20" t="n">
-        <v>3608</v>
+        <v>1324</v>
       </c>
       <c r="E20" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17484</v>
+        <v>163020</v>
       </c>
       <c r="D21" t="n">
-        <v>1060</v>
+        <v>5132</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -906,14 +906,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13113</v>
+        <v>195612</v>
       </c>
       <c r="D22" t="n">
-        <v>936</v>
+        <v>5136</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -928,20 +928,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26130</v>
+        <v>108537</v>
       </c>
       <c r="D23" t="n">
-        <v>1324</v>
+        <v>3608</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -950,17 +950,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>112346</v>
+        <v>50456</v>
       </c>
       <c r="D24" t="n">
-        <v>2700</v>
+        <v>1800</v>
       </c>
       <c r="E24" t="n">
-        <v>377</v>
+        <v>212</v>
       </c>
       <c r="F24" t="n">
         <v>29</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>110558</v>
+        <v>28728</v>
       </c>
       <c r="D25" t="n">
-        <v>2676</v>
+        <v>1364</v>
       </c>
       <c r="E25" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>50456</v>
+        <v>40734</v>
       </c>
       <c r="D26" t="n">
-        <v>1800</v>
+        <v>1620</v>
       </c>
       <c r="E26" t="n">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>33288</v>
+        <v>93066</v>
       </c>
       <c r="D27" t="n">
-        <v>1496</v>
+        <v>2768</v>
       </c>
       <c r="E27" t="n">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c r="F27" t="n">
         <v>29</v>
@@ -1042,15 +1042,59 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>11970</v>
+      </c>
+      <c r="D28" t="n">
+        <v>892</v>
+      </c>
+      <c r="E28" t="n">
+        <v>114</v>
+      </c>
+      <c r="F28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>33288</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1496</v>
+      </c>
+      <c r="E29" t="n">
+        <v>228</v>
+      </c>
+      <c r="F29" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>11180</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D30" t="n">
         <v>864</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E30" t="n">
         <v>130</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>29</v>
       </c>
     </row>

--- a/output/roomself_excel/5581.xlsx
+++ b/output/roomself_excel/5581.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3652</v>
       </c>
-      <c r="E2" t="n">
-        <v>518</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>457</v>
+        <v>428</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>485</v>
+      </c>
+      <c r="J2" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>4252</v>
       </c>
-      <c r="E3" t="n">
-        <v>544</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>140</v>
+        <v>107</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>511</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2716</v>
       </c>
-      <c r="E4" t="n">
-        <v>379</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>359</v>
+        <v>349</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>330</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2656</v>
       </c>
-      <c r="E5" t="n">
-        <v>398</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>324</v>
+        <v>295</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>369</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +647,20 @@
       <c r="D6" t="n">
         <v>2648</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>313</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>30</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +677,20 @@
       <c r="D7" t="n">
         <v>2672</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>373</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +707,20 @@
       <c r="D8" t="n">
         <v>2684</v>
       </c>
-      <c r="E8" t="n">
-        <v>376</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
+        <v>366</v>
+      </c>
+      <c r="G8" t="n">
         <v>29</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +737,20 @@
       <c r="D9" t="n">
         <v>2684</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>375</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>27</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +767,27 @@
       <c r="D10" t="n">
         <v>2680</v>
       </c>
-      <c r="E10" t="n">
-        <v>401</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>374</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>296</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +805,20 @@
       <c r="D11" t="n">
         <v>2700</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>377</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>29</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +835,27 @@
       <c r="D12" t="n">
         <v>2676</v>
       </c>
-      <c r="E12" t="n">
-        <v>398</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>327</v>
+        <v>298</v>
+      </c>
+      <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>371</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +873,20 @@
       <c r="D13" t="n">
         <v>1724</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>245</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>30</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +903,12 @@
       <c r="D14" t="n">
         <v>1028</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +925,12 @@
       <c r="D15" t="n">
         <v>1240</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +947,12 @@
       <c r="D16" t="n">
         <v>1092</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +969,12 @@
       <c r="D17" t="n">
         <v>1316</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +991,12 @@
       <c r="D18" t="n">
         <v>1060</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1013,12 @@
       <c r="D19" t="n">
         <v>936</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1035,12 @@
       <c r="D20" t="n">
         <v>1324</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1057,20 @@
       <c r="D21" t="n">
         <v>5132</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>143</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>29</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1087,12 @@
       <c r="D22" t="n">
         <v>5136</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1109,20 @@
       <c r="D23" t="n">
         <v>3608</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>143</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>27</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1139,20 @@
       <c r="D24" t="n">
         <v>1800</v>
       </c>
-      <c r="E24" t="n">
-        <v>212</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" t="n">
         <v>29</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1169,12 @@
       <c r="D25" t="n">
         <v>1364</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1191,20 @@
       <c r="D26" t="n">
         <v>1620</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>202</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>30</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1221,20 @@
       <c r="D27" t="n">
         <v>2768</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>154</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>29</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1251,20 @@
       <c r="D28" t="n">
         <v>892</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>114</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>27</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1281,20 @@
       <c r="D29" t="n">
         <v>1496</v>
       </c>
-      <c r="E29" t="n">
-        <v>228</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
+        <v>216</v>
+      </c>
+      <c r="G29" t="n">
         <v>29</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1311,20 @@
       <c r="D30" t="n">
         <v>864</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>130</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>29</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
